--- a/Result/profitability/3661.xlsx
+++ b/Result/profitability/3661.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM61"/>
+  <dimension ref="A1:AM62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>17.42</v>
       </c>
       <c r="M2" t="n">
-        <v>18.72875</v>
+        <v>18.4225</v>
       </c>
       <c r="N2" t="n">
-        <v>29.61</v>
+        <v>31.5325</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.99</v>
       </c>
       <c r="M3" t="n">
-        <v>16.045</v>
+        <v>15.65</v>
       </c>
       <c r="N3" t="n">
-        <v>29.875</v>
+        <v>31.5825</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>13.355</v>
+        <v>13.59</v>
       </c>
       <c r="N4" t="n">
-        <v>30.2925</v>
+        <v>31.7525</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -8177,6 +8177,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>7640</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4978</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2662</v>
+      </c>
+      <c r="F62" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1647</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>21.55%</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>388</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2035</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1639</v>
+      </c>
+      <c r="L62" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="M62" t="n">
+        <v>19.0525</v>
+      </c>
+      <c r="N62" t="n">
+        <v>29.96625</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W62" t="n">
+        <v>2.460000000000001</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0.1401709401709401</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>-15.34</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>-0.3056994818652849</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>3.640000000000001</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.2223579718998168</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0.6879844961240311</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK62" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
